--- a/Site Database from Sey.xlsx
+++ b/Site Database from Sey.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Personal\DS&amp;AI\Semester 3\CS5998 Capstone Project\Data\Data from Sey\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C515D4-0EB0-4E01-A1A6-D5EC6BC98CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10DAD54C-D010-4FCE-AE0B-D35B1BB9CD64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{98DD6B9A-3343-4157-9259-E8F5FC5D9560}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Power Breakdown" sheetId="19" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Power Breakdown'!$B$1:$P$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Power Breakdown'!$B$1:$N$76</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,13 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
-  <si>
-    <t>Latitude</t>
-  </si>
-  <si>
-    <t>Longitude</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t>AIRPORT_MAHE</t>
   </si>
@@ -699,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB7CA820-B9CE-475F-8C24-0B20EA4DBB62}">
-  <dimension ref="A1:P230"/>
+  <dimension ref="A1:N230"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.109375" style="4" customWidth="1"/>
@@ -707,61 +701,53 @@
     <col min="3" max="3" width="26.6640625" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="8.88671875" customWidth="1"/>
     <col min="12" max="14" width="12.33203125" customWidth="1"/>
-    <col min="15" max="15" width="11.33203125" customWidth="1"/>
-    <col min="16" max="16" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>76</v>
-      </c>
       <c r="L1" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="N1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="M1" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -769,7 +755,7 @@
         <v>101</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2">
         <v>3</v>
@@ -804,14 +790,8 @@
       <c r="N2" s="2">
         <v>1</v>
       </c>
-      <c r="O2" s="2">
-        <v>-4.671646</v>
-      </c>
-      <c r="P2" s="2">
-        <v>55.513042400000003</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -819,7 +799,7 @@
         <v>102</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2">
         <v>2</v>
@@ -854,14 +834,8 @@
       <c r="N3" s="2">
         <v>0</v>
       </c>
-      <c r="O3" s="2">
-        <v>-4.3240061000000001</v>
-      </c>
-      <c r="P3" s="2">
-        <v>55.6924858</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -869,7 +843,7 @@
         <v>103</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
@@ -904,14 +878,8 @@
       <c r="N4" s="2">
         <v>1</v>
       </c>
-      <c r="O4" s="2">
-        <v>-4.6933049999999996</v>
-      </c>
-      <c r="P4" s="2">
-        <v>55.515804299999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -919,7 +887,7 @@
         <v>104</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -954,14 +922,8 @@
       <c r="N5" s="2">
         <v>0</v>
       </c>
-      <c r="O5" s="2">
-        <v>-4.3517622999999999</v>
-      </c>
-      <c r="P5" s="2">
-        <v>55.7435379</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -969,7 +931,7 @@
         <v>105</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D6" s="2">
         <v>2</v>
@@ -1004,14 +966,8 @@
       <c r="N6" s="2">
         <v>1</v>
       </c>
-      <c r="O6" s="2">
-        <v>-4.6837191999999996</v>
-      </c>
-      <c r="P6" s="2">
-        <v>55.5285072</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1019,7 +975,7 @@
         <v>106</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D7" s="2">
         <v>6</v>
@@ -1054,14 +1010,8 @@
       <c r="N7" s="2">
         <v>1</v>
       </c>
-      <c r="O7" s="2">
-        <v>-4.3045410999999998</v>
-      </c>
-      <c r="P7" s="2">
-        <v>55.6871109</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1069,7 +1019,7 @@
         <v>107</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D8" s="2">
         <v>3</v>
@@ -1104,14 +1054,8 @@
       <c r="N8" s="2">
         <v>1</v>
       </c>
-      <c r="O8" s="2">
-        <v>-4.3388133</v>
-      </c>
-      <c r="P8" s="2">
-        <v>55.833660100000003</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1119,7 +1063,7 @@
         <v>108</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D9" s="2">
         <v>3</v>
@@ -1154,14 +1098,8 @@
       <c r="N9" s="2">
         <v>1</v>
       </c>
-      <c r="O9" s="2">
-        <v>-4.3528856999999999</v>
-      </c>
-      <c r="P9" s="2">
-        <v>55.826458000000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1169,7 +1107,7 @@
         <v>109</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2">
         <v>3</v>
@@ -1204,14 +1142,8 @@
       <c r="N10" s="2">
         <v>1</v>
       </c>
-      <c r="O10" s="2">
-        <v>-4.3161205999999996</v>
-      </c>
-      <c r="P10" s="2">
-        <v>55.7459755</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1219,7 +1151,7 @@
         <v>110</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D11" s="2">
         <v>3</v>
@@ -1254,14 +1186,8 @@
       <c r="N11" s="2">
         <v>1</v>
       </c>
-      <c r="O11" s="2">
-        <v>-4.747268</v>
-      </c>
-      <c r="P11" s="2">
-        <v>55.465781</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1269,7 +1195,7 @@
         <v>111</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2">
         <v>3</v>
@@ -1304,14 +1230,8 @@
       <c r="N12" s="2">
         <v>0</v>
       </c>
-      <c r="O12" s="2">
-        <v>-4.6907240000000003</v>
-      </c>
-      <c r="P12" s="2">
-        <v>55.4736671</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1319,7 +1239,7 @@
         <v>112</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D13" s="2">
         <v>5</v>
@@ -1354,14 +1274,8 @@
       <c r="N13" s="2">
         <v>1</v>
       </c>
-      <c r="O13" s="2">
-        <v>-4.6755319999999996</v>
-      </c>
-      <c r="P13" s="2">
-        <v>55.459494999999997</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1369,7 +1283,7 @@
         <v>113</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2">
         <v>5</v>
@@ -1404,14 +1318,8 @@
       <c r="N14" s="2">
         <v>1</v>
       </c>
-      <c r="O14" s="2">
-        <v>-4.6177324999999998</v>
-      </c>
-      <c r="P14" s="2">
-        <v>55.428901699999997</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1419,7 +1327,7 @@
         <v>114</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D15" s="2">
         <v>3</v>
@@ -1454,14 +1362,8 @@
       <c r="N15" s="2">
         <v>0</v>
       </c>
-      <c r="O15" s="2">
-        <v>-4.6213517</v>
-      </c>
-      <c r="P15" s="2">
-        <v>55.403133400000002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1469,7 +1371,7 @@
         <v>115</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D16" s="2">
         <v>3</v>
@@ -1504,14 +1406,8 @@
       <c r="N16" s="2">
         <v>0</v>
       </c>
-      <c r="O16" s="2">
-        <v>-4.6699270999999998</v>
-      </c>
-      <c r="P16" s="2">
-        <v>55.428508800000003</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1519,7 +1415,7 @@
         <v>116</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D17" s="2">
         <v>3</v>
@@ -1554,14 +1450,8 @@
       <c r="N17" s="2">
         <v>0</v>
       </c>
-      <c r="O17" s="2">
-        <v>-4.7072601000000001</v>
-      </c>
-      <c r="P17" s="2">
-        <v>55.499893200000002</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1569,7 +1459,7 @@
         <v>117</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D18" s="2">
         <v>5</v>
@@ -1604,14 +1494,8 @@
       <c r="N18" s="2">
         <v>1</v>
       </c>
-      <c r="O18" s="2">
-        <v>-4.5697369999999999</v>
-      </c>
-      <c r="P18" s="2">
-        <v>55.453796400000002</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1619,7 +1503,7 @@
         <v>118</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D19" s="2">
         <v>3</v>
@@ -1654,14 +1538,8 @@
       <c r="N19" s="2">
         <v>1</v>
       </c>
-      <c r="O19" s="2">
-        <v>-4.6233610000000001</v>
-      </c>
-      <c r="P19" s="2">
-        <v>55.454000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1669,7 +1547,7 @@
         <v>119</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D20" s="2">
         <v>3</v>
@@ -1704,14 +1582,8 @@
       <c r="N20" s="2">
         <v>1</v>
       </c>
-      <c r="O20" s="2">
-        <v>-4.6314719999999996</v>
-      </c>
-      <c r="P20" s="2">
-        <v>55.496082999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1719,7 +1591,7 @@
         <v>120</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D21" s="2">
         <v>3</v>
@@ -1754,14 +1626,8 @@
       <c r="N21" s="2">
         <v>1</v>
       </c>
-      <c r="O21" s="2">
-        <v>-4.3698645000000003</v>
-      </c>
-      <c r="P21" s="2">
-        <v>55.833980599999997</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1769,7 +1635,7 @@
         <v>121</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D22" s="2">
         <v>3</v>
@@ -1804,14 +1670,8 @@
       <c r="N22" s="2">
         <v>1</v>
       </c>
-      <c r="O22" s="2">
-        <v>-4.6261581999999999</v>
-      </c>
-      <c r="P22" s="2">
-        <v>55.452854199999997</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1819,7 +1679,7 @@
         <v>122</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D23" s="2">
         <v>3</v>
@@ -1854,14 +1714,8 @@
       <c r="N23" s="2">
         <v>1</v>
       </c>
-      <c r="O23" s="2">
-        <v>-4.6443029999999998</v>
-      </c>
-      <c r="P23" s="2">
-        <v>55.474387</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1869,7 +1723,7 @@
         <v>123</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D24" s="2">
         <v>3</v>
@@ -1904,14 +1758,8 @@
       <c r="N24" s="2">
         <v>0</v>
       </c>
-      <c r="O24" s="2">
-        <v>-4.6556115</v>
-      </c>
-      <c r="P24" s="2">
-        <v>55.405384099999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1919,7 +1767,7 @@
         <v>124</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D25" s="2">
         <v>4</v>
@@ -1954,14 +1802,8 @@
       <c r="N25" s="2">
         <v>1</v>
       </c>
-      <c r="O25" s="2">
-        <v>-4.7549548000000001</v>
-      </c>
-      <c r="P25" s="2">
-        <v>55.479370099999997</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1969,7 +1811,7 @@
         <v>125</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -2004,14 +1846,8 @@
       <c r="N26" s="2">
         <v>0</v>
       </c>
-      <c r="O26" s="2">
-        <v>-4.7579421999999996</v>
-      </c>
-      <c r="P26" s="2">
-        <v>55.464759800000003</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2019,7 +1855,7 @@
         <v>126</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -2054,14 +1890,8 @@
       <c r="N27" s="2">
         <v>0</v>
       </c>
-      <c r="O27" s="2">
-        <v>-4.5818899999999996</v>
-      </c>
-      <c r="P27" s="2">
-        <v>55.935896999999997</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -2069,7 +1899,7 @@
         <v>127</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D28" s="2">
         <v>2</v>
@@ -2104,14 +1934,8 @@
       <c r="N28" s="2">
         <v>1</v>
       </c>
-      <c r="O28" s="2">
-        <v>-4.7040372000000001</v>
-      </c>
-      <c r="P28" s="2">
-        <v>55.510734599999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2119,7 +1943,7 @@
         <v>128</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D29" s="2">
         <v>3</v>
@@ -2154,14 +1978,8 @@
       <c r="N29" s="2">
         <v>1</v>
       </c>
-      <c r="O29" s="2">
-        <v>-4.3270949999999999</v>
-      </c>
-      <c r="P29" s="2">
-        <v>55.714134199999997</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2169,7 +1987,7 @@
         <v>129</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D30" s="2">
         <v>3</v>
@@ -2204,14 +2022,8 @@
       <c r="N30" s="2">
         <v>0</v>
       </c>
-      <c r="O30" s="2">
-        <v>-4.3063396999999997</v>
-      </c>
-      <c r="P30" s="2">
-        <v>55.706897699999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2219,7 +2031,7 @@
         <v>130</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D31" s="2">
         <v>6</v>
@@ -2254,14 +2066,8 @@
       <c r="N31" s="2">
         <v>1</v>
       </c>
-      <c r="O31" s="2">
-        <v>-4.6292972222222204</v>
-      </c>
-      <c r="P31" s="2">
-        <v>55.460508333333301</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2269,7 +2075,7 @@
         <v>132</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D32" s="2">
         <v>4</v>
@@ -2304,14 +2110,8 @@
       <c r="N32" s="2">
         <v>0</v>
       </c>
-      <c r="O32" s="2">
-        <v>-4.7856649999999998</v>
-      </c>
-      <c r="P32" s="2">
-        <v>55.505312000000004</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -2319,7 +2119,7 @@
         <v>133</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D33" s="2">
         <v>3</v>
@@ -2354,14 +2154,8 @@
       <c r="N33" s="2">
         <v>1</v>
       </c>
-      <c r="O33" s="2">
-        <v>-4.5850482000000001</v>
-      </c>
-      <c r="P33" s="2">
-        <v>55.454063400000003</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -2369,7 +2163,7 @@
         <v>134</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D34" s="2">
         <v>3</v>
@@ -2404,14 +2198,8 @@
       <c r="N34" s="2">
         <v>1</v>
       </c>
-      <c r="O34" s="2">
-        <v>-4.6701984000000003</v>
-      </c>
-      <c r="P34" s="2">
-        <v>55.473995199999997</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -2419,7 +2207,7 @@
         <v>135</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D35" s="2">
         <v>3</v>
@@ -2454,14 +2242,8 @@
       <c r="N35" s="2">
         <v>1</v>
       </c>
-      <c r="O35" s="2">
-        <v>-4.7235861000000003</v>
-      </c>
-      <c r="P35" s="2">
-        <v>55.483875300000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -2469,7 +2251,7 @@
         <v>136</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D36" s="2">
         <v>3</v>
@@ -2504,14 +2286,8 @@
       <c r="N36" s="2">
         <v>1</v>
       </c>
-      <c r="O36" s="2">
-        <v>-4.6258454000000002</v>
-      </c>
-      <c r="P36" s="2">
-        <v>55.426067400000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2519,7 +2295,7 @@
         <v>137</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D37" s="2">
         <v>3</v>
@@ -2554,14 +2330,8 @@
       <c r="N37" s="2">
         <v>1</v>
       </c>
-      <c r="O37" s="2">
-        <v>-4.6480293000000001</v>
-      </c>
-      <c r="P37" s="2">
-        <v>55.472999600000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -2569,7 +2339,7 @@
         <v>138</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D38" s="2">
         <v>4</v>
@@ -2604,14 +2374,8 @@
       <c r="N38" s="2">
         <v>1</v>
       </c>
-      <c r="O38" s="2">
-        <v>-4.7367834999999996</v>
-      </c>
-      <c r="P38" s="2">
-        <v>55.5063934</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2619,7 +2383,7 @@
         <v>139</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D39" s="2">
         <v>3</v>
@@ -2654,14 +2418,8 @@
       <c r="N39" s="2">
         <v>1</v>
       </c>
-      <c r="O39" s="2">
-        <v>-4.6061300000000003</v>
-      </c>
-      <c r="P39" s="2">
-        <v>55.45543</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2669,7 +2427,7 @@
         <v>140</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D40" s="2">
         <v>4</v>
@@ -2704,14 +2462,8 @@
       <c r="N40" s="2">
         <v>0</v>
       </c>
-      <c r="O40" s="2">
-        <v>-4.5639238000000004</v>
-      </c>
-      <c r="P40" s="2">
-        <v>55.438999199999998</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -2719,7 +2471,7 @@
         <v>141</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D41" s="2">
         <v>3</v>
@@ -2754,14 +2506,8 @@
       <c r="N41" s="2">
         <v>0</v>
       </c>
-      <c r="O41" s="2">
-        <v>-4.3921390000000002</v>
-      </c>
-      <c r="P41" s="2">
-        <v>55.242832999999997</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -2769,7 +2515,7 @@
         <v>142</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D42" s="2">
         <v>4</v>
@@ -2804,14 +2550,8 @@
       <c r="N42" s="2">
         <v>1</v>
       </c>
-      <c r="O42" s="2">
-        <v>-4.5823869999999998</v>
-      </c>
-      <c r="P42" s="2">
-        <v>55.433751999999998</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2819,7 +2559,7 @@
         <v>144</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D43" s="2">
         <v>3</v>
@@ -2854,14 +2594,8 @@
       <c r="N43" s="2">
         <v>1</v>
       </c>
-      <c r="O43" s="2">
-        <v>-4.7316813</v>
-      </c>
-      <c r="P43" s="2">
-        <v>55.520557400000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -2869,7 +2603,7 @@
         <v>145</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D44" s="2">
         <v>3</v>
@@ -2904,14 +2638,8 @@
       <c r="N44" s="2">
         <v>1</v>
       </c>
-      <c r="O44" s="2">
-        <v>-4.3432120000000003</v>
-      </c>
-      <c r="P44" s="2">
-        <v>55.758389999999999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -2919,7 +2647,7 @@
         <v>146</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D45" s="2">
         <v>3</v>
@@ -2954,14 +2682,8 @@
       <c r="N45" s="2">
         <v>0</v>
       </c>
-      <c r="O45" s="2">
-        <v>-4.3080772999999999</v>
-      </c>
-      <c r="P45" s="2">
-        <v>55.737220800000003</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2969,7 +2691,7 @@
         <v>147</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D46" s="2">
         <v>3</v>
@@ -3004,14 +2726,8 @@
       <c r="N46" s="2">
         <v>1</v>
       </c>
-      <c r="O46" s="2">
-        <v>-4.6558460000000004</v>
-      </c>
-      <c r="P46" s="2">
-        <v>55.488559000000002</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -3019,7 +2735,7 @@
         <v>148</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D47" s="2">
         <v>5</v>
@@ -3054,14 +2770,8 @@
       <c r="N47" s="2">
         <v>0</v>
       </c>
-      <c r="O47" s="2">
-        <v>-4.3252201000000001</v>
-      </c>
-      <c r="P47" s="2">
-        <v>55.7537041</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -3069,7 +2779,7 @@
         <v>149</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D48" s="2">
         <v>3</v>
@@ -3104,14 +2814,8 @@
       <c r="N48" s="2">
         <v>1</v>
       </c>
-      <c r="O48" s="2">
-        <v>-4.6328082000000004</v>
-      </c>
-      <c r="P48" s="2">
-        <v>55.467685699999997</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -3119,7 +2823,7 @@
         <v>150</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D49" s="2">
         <v>3</v>
@@ -3154,14 +2858,8 @@
       <c r="N49" s="2">
         <v>1</v>
       </c>
-      <c r="O49" s="2">
-        <v>-4.6199621999999998</v>
-      </c>
-      <c r="P49" s="2">
-        <v>55.454093899999997</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -3169,7 +2867,7 @@
         <v>151</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D50" s="2">
         <v>3</v>
@@ -3204,14 +2902,8 @@
       <c r="N50" s="2">
         <v>1</v>
       </c>
-      <c r="O50" s="2">
-        <v>-4.6205287000000004</v>
-      </c>
-      <c r="P50" s="2">
-        <v>55.441398599999999</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -3219,7 +2911,7 @@
         <v>152</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D51" s="2">
         <v>3</v>
@@ -3254,14 +2946,8 @@
       <c r="N51" s="2">
         <v>1</v>
       </c>
-      <c r="O51" s="2">
-        <v>-4.605556</v>
-      </c>
-      <c r="P51" s="2">
-        <v>55.505833000000003</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -3269,7 +2955,7 @@
         <v>153</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D52" s="2">
         <v>4</v>
@@ -3304,14 +2990,8 @@
       <c r="N52" s="2">
         <v>0</v>
       </c>
-      <c r="O52" s="2">
-        <v>-4.6326746180000002</v>
-      </c>
-      <c r="P52" s="2">
-        <v>55.44895846</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -3319,7 +2999,7 @@
         <v>154</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D53" s="2">
         <v>2</v>
@@ -3354,14 +3034,8 @@
       <c r="N53" s="2">
         <v>0</v>
       </c>
-      <c r="O53" s="2">
-        <v>-4.4834630000000004</v>
-      </c>
-      <c r="P53" s="2">
-        <v>55.250197</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -3369,7 +3043,7 @@
         <v>155</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D54" s="2">
         <v>3</v>
@@ -3404,14 +3078,8 @@
       <c r="N54" s="2">
         <v>1</v>
       </c>
-      <c r="O54" s="2">
-        <v>-4.6121809999999996</v>
-      </c>
-      <c r="P54" s="2">
-        <v>55.498075</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -3419,7 +3087,7 @@
         <v>156</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D55" s="2">
         <v>3</v>
@@ -3454,14 +3122,8 @@
       <c r="N55" s="2">
         <v>1</v>
       </c>
-      <c r="O55" s="2">
-        <v>-4.6513314000000001</v>
-      </c>
-      <c r="P55" s="2">
-        <v>55.4841652</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -3469,7 +3131,7 @@
         <v>157</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D56" s="2">
         <v>3</v>
@@ -3504,14 +3166,8 @@
       <c r="N56" s="2">
         <v>1</v>
       </c>
-      <c r="O56" s="2">
-        <v>-4.7835320000000001</v>
-      </c>
-      <c r="P56" s="2">
-        <v>55.514465999999999</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -3519,7 +3175,7 @@
         <v>158</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D57" s="2">
         <v>1</v>
@@ -3554,14 +3210,8 @@
       <c r="N57" s="2">
         <v>0</v>
       </c>
-      <c r="O57" s="2">
-        <v>-4.7556070999999998</v>
-      </c>
-      <c r="P57" s="2">
-        <v>55.498443600000002</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -3569,7 +3219,7 @@
         <v>160</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D58" s="2">
         <v>3</v>
@@ -3604,14 +3254,8 @@
       <c r="N58" s="2">
         <v>1</v>
       </c>
-      <c r="O58" s="2">
-        <v>-4.6142349999999999</v>
-      </c>
-      <c r="P58" s="2">
-        <v>55.457518</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -3619,7 +3263,7 @@
         <v>161</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D59" s="2">
         <v>1</v>
@@ -3654,14 +3298,8 @@
       <c r="N59" s="2">
         <v>0</v>
       </c>
-      <c r="O59" s="2">
-        <v>-4.6380100000000004</v>
-      </c>
-      <c r="P59" s="2">
-        <v>55.455300000000001</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -3669,7 +3307,7 @@
         <v>162</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D60" s="2">
         <v>3</v>
@@ -3704,14 +3342,8 @@
       <c r="N60" s="2">
         <v>1</v>
       </c>
-      <c r="O60" s="2">
-        <v>-4.6144860000000003</v>
-      </c>
-      <c r="P60" s="2">
-        <v>55.451642999999997</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -3719,7 +3351,7 @@
         <v>163</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D61" s="2">
         <v>0</v>
@@ -3754,14 +3386,8 @@
       <c r="N61" s="2">
         <v>1</v>
       </c>
-      <c r="O61" s="2">
-        <v>-4.6695700000000002</v>
-      </c>
-      <c r="P61" s="2">
-        <v>55.501440000000002</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -3769,7 +3395,7 @@
         <v>165</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D62" s="2">
         <v>0</v>
@@ -3804,14 +3430,8 @@
       <c r="N62" s="2">
         <v>1</v>
       </c>
-      <c r="O62" s="2">
-        <v>-4.6428051000000004</v>
-      </c>
-      <c r="P62" s="2">
-        <v>55.459307500000001</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -3819,7 +3439,7 @@
         <v>166</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D63" s="2">
         <v>0</v>
@@ -3854,14 +3474,8 @@
       <c r="N63" s="2">
         <v>0</v>
       </c>
-      <c r="O63" s="2">
-        <v>-4.7321679999999997</v>
-      </c>
-      <c r="P63" s="2">
-        <v>55.491436999999998</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -3869,7 +3483,7 @@
         <v>168</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D64" s="2">
         <v>0</v>
@@ -3904,14 +3518,8 @@
       <c r="N64" s="2">
         <v>0</v>
       </c>
-      <c r="O64" s="2">
-        <v>-4.7423000000000002</v>
-      </c>
-      <c r="P64" s="2">
-        <v>55.511749999999999</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -3919,7 +3527,7 @@
         <v>170</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D65" s="2">
         <v>0</v>
@@ -3954,14 +3562,8 @@
       <c r="N65" s="2">
         <v>1</v>
       </c>
-      <c r="O65" s="2">
-        <v>-4.6077219999999999</v>
-      </c>
-      <c r="P65" s="2">
-        <v>55.468781999999997</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -3969,7 +3571,7 @@
         <v>172</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D66" s="2">
         <v>0</v>
@@ -4004,14 +3606,8 @@
       <c r="N66" s="2">
         <v>1</v>
       </c>
-      <c r="O66" s="2">
-        <v>-4.6361910000000002</v>
-      </c>
-      <c r="P66" s="2">
-        <v>55.471066999999998</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -4019,7 +3615,7 @@
         <v>173</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D67" s="2">
         <v>0</v>
@@ -4054,14 +3650,8 @@
       <c r="N67" s="2">
         <v>1</v>
       </c>
-      <c r="O67" s="2">
-        <v>-4.3429390000000003</v>
-      </c>
-      <c r="P67" s="2">
-        <v>55.762785000000001</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -4069,7 +3659,7 @@
         <v>174</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D68" s="2">
         <v>0</v>
@@ -4104,14 +3694,8 @@
       <c r="N68" s="2">
         <v>1</v>
       </c>
-      <c r="O68" s="2">
-        <v>-4.5750409999999997</v>
-      </c>
-      <c r="P68" s="2">
-        <v>55.434286999999998</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -4119,7 +3703,7 @@
         <v>175</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D69" s="2">
         <v>0</v>
@@ -4154,14 +3738,8 @@
       <c r="N69" s="2">
         <v>1</v>
       </c>
-      <c r="O69" s="2">
-        <v>-4.6402679999999998</v>
-      </c>
-      <c r="P69" s="2">
-        <v>55.476776000000001</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -4169,7 +3747,7 @@
         <v>183</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D70" s="2">
         <v>0</v>
@@ -4204,14 +3782,8 @@
       <c r="N70" s="2">
         <v>1</v>
       </c>
-      <c r="O70" s="2">
-        <v>-4.6044429999999998</v>
-      </c>
-      <c r="P70" s="2">
-        <v>55.462600999999999</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -4219,7 +3791,7 @@
         <v>184</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D71" s="2">
         <v>0</v>
@@ -4254,14 +3826,8 @@
       <c r="N71" s="2">
         <v>0</v>
       </c>
-      <c r="O71" s="2">
-        <v>-4.6750999999999996</v>
-      </c>
-      <c r="P71" s="2">
-        <v>55.516205999999997</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -4269,7 +3835,7 @@
         <v>186</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D72" s="2">
         <v>0</v>
@@ -4304,14 +3870,8 @@
       <c r="N72" s="2">
         <v>0</v>
       </c>
-      <c r="O72" s="2">
-        <v>-4.3395099999999998</v>
-      </c>
-      <c r="P72" s="2">
-        <v>55.762346000000001</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -4319,7 +3879,7 @@
         <v>167</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D73" s="2">
         <v>0</v>
@@ -4354,14 +3914,8 @@
       <c r="N73" s="2">
         <v>0</v>
       </c>
-      <c r="O73" s="2">
-        <v>-4.6395530000000003</v>
-      </c>
-      <c r="P73" s="2">
-        <v>55.465620000000001</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -4369,7 +3923,7 @@
         <v>169</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D74" s="2">
         <v>0</v>
@@ -4404,14 +3958,8 @@
       <c r="N74" s="2">
         <v>0</v>
       </c>
-      <c r="O74" s="2">
-        <v>-4.6226130000000003</v>
-      </c>
-      <c r="P74" s="2">
-        <v>55.451205999999999</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -4419,7 +3967,7 @@
         <v>176</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D75" s="2">
         <v>0</v>
@@ -4454,14 +4002,8 @@
       <c r="N75" s="2">
         <v>0</v>
       </c>
-      <c r="O75" s="2">
-        <v>-4.60589651</v>
-      </c>
-      <c r="P75" s="2">
-        <v>55.433000130000003</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -4469,7 +4011,7 @@
         <v>187</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D76" s="2">
         <v>2</v>
@@ -4504,26 +4046,20 @@
       <c r="N76" s="2">
         <v>0</v>
       </c>
-      <c r="O76" s="2">
-        <v>-4.755147</v>
-      </c>
-      <c r="P76" s="2">
-        <v>55.475555999999997</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B77"/>
       <c r="C77"/>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B78"/>
       <c r="C78"/>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B79"/>
       <c r="C79"/>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B80"/>
       <c r="C80"/>
     </row>
@@ -5128,7 +4664,7 @@
       <c r="C230"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:P76" xr:uid="{BB7CA820-B9CE-475F-8C24-0B20EA4DBB62}"/>
+  <autoFilter ref="B1:N76" xr:uid="{BB7CA820-B9CE-475F-8C24-0B20EA4DBB62}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5136,17 +4672,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="034e0dd5-fed9-4339-924b-d9a4289dd1af" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3dded61f-7458-4aa1-8de7-730befce5d1c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004373D94923650A4080F1D7AC8E70CAEF" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="87e62d68363af4283ee618e788c983e4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3dded61f-7458-4aa1-8de7-730befce5d1c" xmlns:ns3="034e0dd5-fed9-4339-924b-d9a4289dd1af" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f8eec4e40121be174acadf5edb47d338" ns2:_="" ns3:_="">
     <xsd:import namespace="3dded61f-7458-4aa1-8de7-730befce5d1c"/>
@@ -5401,6 +4926,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="034e0dd5-fed9-4339-924b-d9a4289dd1af" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3dded61f-7458-4aa1-8de7-730befce5d1c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5411,17 +4947,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{818F8FA1-34D3-41E2-A6E2-4E11EDB9B716}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="034e0dd5-fed9-4339-924b-d9a4289dd1af"/>
-    <ds:schemaRef ds:uri="3dded61f-7458-4aa1-8de7-730befce5d1c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DF7DFA6-651C-4F54-9C54-E813C876269E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5440,6 +4965,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{818F8FA1-34D3-41E2-A6E2-4E11EDB9B716}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="034e0dd5-fed9-4339-924b-d9a4289dd1af"/>
+    <ds:schemaRef ds:uri="3dded61f-7458-4aa1-8de7-730befce5d1c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B115DB5-12B9-4FBF-8C30-7F8792041D10}">
   <ds:schemaRefs>
